--- a/data/satisfaction_detail/2026/1-8月/自助餐.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/自助餐.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.42</v>
+        <v>9.601618507793727</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.68</v>
+        <v>9.78622820528618</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.82</v>
+        <v>9.818643336824593</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.99</v>
+        <v>9.980075164808083</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.92</v>
+        <v>9.857679748629165</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>10</v>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.92</v>
+        <v>9.857679748629165</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.4</v>
+        <v>9.540305588072208</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10</v>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.44</v>
+        <v>9.613702174850593</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.92</v>
+        <v>9.857679748629165</v>
       </c>
     </row>
     <row r="8">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.84</v>
+        <v>9.814475386605876</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>10</v>
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>9.01</v>
+        <v>9.381557513400281</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>9.589040108434476</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.379383634431456</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8.6</v>
+        <v>8.825717321997875</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.48</v>
+        <v>9.640810794159325</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.798379643891318</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.359999999999999</v>
+        <v>9.535459922370773</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.717731501447846</v>
       </c>
     </row>
     <row r="16">
